--- a/config/Coding/VF5NP_ACM_CDS.xlsx
+++ b/config/Coding/VF5NP_ACM_CDS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\REDO\CODINGTOOL\config\Coding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D455BDDA-72A4-43DA-9F9D-5C2CACC235FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C5DEC9D-1B4F-4AE3-8BB8-61024D0C4FF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ABFBD026-99C8-4534-880F-EF7C8CBF5F13}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23232" windowHeight="12432" xr2:uid="{ABFBD026-99C8-4534-880F-EF7C8CBF5F13}"/>
   </bookViews>
   <sheets>
     <sheet name="CDS Coding" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,6 @@
     <externalReference r:id="rId15"/>
     <externalReference r:id="rId16"/>
     <externalReference r:id="rId17"/>
-    <externalReference r:id="rId18"/>
   </externalReferences>
   <definedNames>
     <definedName name="\">#N/A</definedName>
@@ -759,7 +758,7 @@
     <definedName name="AA\\\\\">#REF!</definedName>
     <definedName name="AA\\\\\\">#REF!</definedName>
     <definedName name="AAA">#REF!</definedName>
-    <definedName name="aaaa">[2]Selections!$A$2:$A$103</definedName>
+    <definedName name="aaaa">[1]Selections!$A$2:$A$103</definedName>
     <definedName name="aaaaa" localSheetId="0" hidden="1">{"RES-2000",#N/A,FALSE,"BL2000";"A1-2000",#N/A,FALSE,"BL2000";"A2-2000",#N/A,FALSE,"BL2000"}</definedName>
     <definedName name="aaaaa" hidden="1">{"RES-2000",#N/A,FALSE,"BL2000";"A1-2000",#N/A,FALSE,"BL2000";"A2-2000",#N/A,FALSE,"BL2000"}</definedName>
     <definedName name="aaaaaa" localSheetId="0" hidden="1">{"RES-2002",#N/A,FALSE,"BL2000";"A1-2002",#N/A,FALSE,"BL2000";"A2-2002",#N/A,FALSE,"BL2000"}</definedName>
@@ -780,8 +779,8 @@
     <definedName name="aaaaaaaaaaaaaaaaa" hidden="1">{"AnaM1",#N/A,FALSE,"AnalisisM";"AnaM2",#N/A,FALSE,"AnalisisM";"AnaM3",#N/A,FALSE,"AnalisisM"}</definedName>
     <definedName name="aaaaaaaaaaaaaaaaaaaaaaaa" localSheetId="0" hidden="1">{"COMJPN2000",#N/A,FALSE,"BL2000"}</definedName>
     <definedName name="aaaaaaaaaaaaaaaaaaaaaaaa" hidden="1">{"COMJPN2000",#N/A,FALSE,"BL2000"}</definedName>
-    <definedName name="aaab">[2]Selections!$A$2:$A$103</definedName>
-    <definedName name="aac">[2]Selections!$A$2:$A$103</definedName>
+    <definedName name="aaab">[1]Selections!$A$2:$A$103</definedName>
+    <definedName name="aac">[1]Selections!$A$2:$A$103</definedName>
     <definedName name="ab" localSheetId="0" hidden="1">{"HS_USA",#N/A,FALSE,"Base"}</definedName>
     <definedName name="ab" hidden="1">{"HS_USA",#N/A,FALSE,"Base"}</definedName>
     <definedName name="ABC" localSheetId="0" hidden="1">{"INCPRE2000",#N/A,FALSE,"BL2000"}</definedName>
@@ -792,7 +791,7 @@
     <definedName name="ABRIL">#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!</definedName>
     <definedName name="abs">#REF!</definedName>
     <definedName name="Acc">#REF!</definedName>
-    <definedName name="Access_Attribute">[2]Selections!$H$2:$H$4</definedName>
+    <definedName name="Access_Attribute">[1]Selections!$H$2:$H$4</definedName>
     <definedName name="Access_Button" hidden="1">"機能ｺｰﾄﾞ一覧_BLK→機能_List"</definedName>
     <definedName name="Access_Button1" hidden="1">"機能ｺｰﾄﾞ一覧_BLK→機能_List"</definedName>
     <definedName name="Access_Button2" hidden="1">"機能ｺｰﾄﾞ一覧_BLK→機能_List"</definedName>
@@ -811,7 +810,7 @@
     <definedName name="AIAOYE">InpMove7</definedName>
     <definedName name="AK">#REF!</definedName>
     <definedName name="ALE">#REF!</definedName>
-    <definedName name="Alert_Behaviour">[2]Selections!$G$2:$G$7</definedName>
+    <definedName name="Alert_Behaviour">[1]Selections!$G$2:$G$7</definedName>
     <definedName name="ALG_24">#REF!</definedName>
     <definedName name="ALG_24_low">#REF!</definedName>
     <definedName name="ALG_24_Std">#REF!</definedName>
@@ -851,8 +850,8 @@
     <definedName name="APR_Program_Pen">#REF!</definedName>
     <definedName name="apr_retail">#REF!</definedName>
     <definedName name="april">#REF!</definedName>
-    <definedName name="Area" localSheetId="0">[3]Selections!$I$1:$I$2</definedName>
-    <definedName name="Area">[4]Selections!$I$1:$I$2</definedName>
+    <definedName name="Area" localSheetId="0">[2]Selections!$I$1:$I$2</definedName>
+    <definedName name="Area">[3]Selections!$I$1:$I$2</definedName>
     <definedName name="AREA_COVER">#REF!</definedName>
     <definedName name="Arial">#REF!</definedName>
     <definedName name="as">#REF!</definedName>
@@ -867,8 +866,8 @@
     <definedName name="ATTACH4">#REF!</definedName>
     <definedName name="Attachment">#REF!</definedName>
     <definedName name="Attachment_4_all">#REF!</definedName>
-    <definedName name="Audience" localSheetId="0">[3]Selections!$C$1:$C$7</definedName>
-    <definedName name="Audience">[4]Selections!$C$1:$C$7</definedName>
+    <definedName name="Audience" localSheetId="0">[2]Selections!$C$1:$C$7</definedName>
+    <definedName name="Audience">[3]Selections!$C$1:$C$7</definedName>
     <definedName name="august">#REF!</definedName>
     <definedName name="B">#REF!</definedName>
     <definedName name="B\">#REF!</definedName>
@@ -922,7 +921,7 @@
     <definedName name="CHARTCURRENY">#REF!</definedName>
     <definedName name="check">#REF!</definedName>
     <definedName name="CHECK_1">"チェック 65"</definedName>
-    <definedName name="Check_Per_Cycle">[2]Selections!$J$2:$J$4</definedName>
+    <definedName name="Check_Per_Cycle">[1]Selections!$J$2:$J$4</definedName>
     <definedName name="Chicago">#REF!</definedName>
     <definedName name="cmprtl_dir">#REF!</definedName>
     <definedName name="Ｃｏ">#REF!</definedName>
@@ -1007,8 +1006,8 @@
     <definedName name="Dealer_Gross_Lease">#REF!</definedName>
     <definedName name="Dealer_Gross_Retail">#REF!</definedName>
     <definedName name="december">#REF!</definedName>
-    <definedName name="Decode_Type" localSheetId="0">[3]Selections!$F$1:$F$9</definedName>
-    <definedName name="Decode_Type">[4]Selections!$F$1:$F$9</definedName>
+    <definedName name="Decode_Type" localSheetId="0">[2]Selections!$F$1:$F$9</definedName>
+    <definedName name="Decode_Type">[3]Selections!$F$1:$F$9</definedName>
     <definedName name="Desc">#REF!</definedName>
     <definedName name="DEST">#REF!</definedName>
     <definedName name="ｄｆｄ" localSheetId="0">InpMove1</definedName>
@@ -1024,8 +1023,8 @@
     <definedName name="ＤＨ">#REF!</definedName>
     <definedName name="Di">#REF!</definedName>
     <definedName name="DIC">#REF!</definedName>
-    <definedName name="DID_Group" localSheetId="0">[3]Selections!$E$1:$E$6</definedName>
-    <definedName name="DID_Group">[4]Selections!$E$1:$E$6</definedName>
+    <definedName name="DID_Group" localSheetId="0">[2]Selections!$E$1:$E$6</definedName>
+    <definedName name="DID_Group">[3]Selections!$E$1:$E$6</definedName>
     <definedName name="digit_18">"テキスト 21"</definedName>
     <definedName name="Dimax">#REF!</definedName>
     <definedName name="Dimin">#REF!</definedName>
@@ -1054,7 +1053,7 @@
     <definedName name="DSFGSDFG">#REF!</definedName>
     <definedName name="dsfsf" localSheetId="0" hidden="1">{"SUM GER",#N/A,FALSE,"SUM GER";"SUM FRA",#N/A,FALSE,"SUM FRA";"SUM ITA",#N/A,FALSE,"SUM ITA";"SUM SPA",#N/A,FALSE,"SUM SPA";"SUM EGB",#N/A,FALSE,"SUM EGB";"SUM IND",#N/A,FALSE,"SUM IND"}</definedName>
     <definedName name="dsfsf" hidden="1">{"SUM GER",#N/A,FALSE,"SUM GER";"SUM FRA",#N/A,FALSE,"SUM FRA";"SUM ITA",#N/A,FALSE,"SUM ITA";"SUM SPA",#N/A,FALSE,"SUM SPA";"SUM EGB",#N/A,FALSE,"SUM EGB";"SUM IND",#N/A,FALSE,"SUM IND"}</definedName>
-    <definedName name="DTC_Class">[2]Selections!$F$2:$F$7</definedName>
+    <definedName name="DTC_Class">[1]Selections!$F$2:$F$7</definedName>
     <definedName name="DTEXT">#REF!</definedName>
     <definedName name="DUMMY">#REF!</definedName>
     <definedName name="ｄふぇｄふぇ" localSheetId="0">InpMove3</definedName>
@@ -1072,7 +1071,7 @@
     <definedName name="E50ﾄﾞﾗﾍﾙ西端" hidden="1">1</definedName>
     <definedName name="Eb">#REF!</definedName>
     <definedName name="EcartFranchise">#REF!</definedName>
-    <definedName name="ECUDID1">[5]Selections!$I$1:$I$2</definedName>
+    <definedName name="ECUDID1">[4]Selections!$I$1:$I$2</definedName>
     <definedName name="EE">#REF!</definedName>
     <definedName name="EE\">#REF!</definedName>
     <definedName name="EE\\">#REF!</definedName>
@@ -1155,7 +1154,7 @@
     <definedName name="FactoryResultUpdate">#REF!</definedName>
     <definedName name="fasdf" localSheetId="0" hidden="1">{"SUM ALL YR",#N/A,FALSE,"SUM ALL YR";"sum01",#N/A,FALSE,"SUM 01";"sumM2",#N/A,FALSE,"SUM M2";"sum02",#N/A,FALSE,"SUM 02";"sum03",#N/A,FALSE,"SUM 03";"sum04",#N/A,FALSE,"SUM 04";"sum05",#N/A,FALSE,"SUM 05"}</definedName>
     <definedName name="fasdf" hidden="1">{"SUM ALL YR",#N/A,FALSE,"SUM ALL YR";"sum01",#N/A,FALSE,"SUM 01";"sumM2",#N/A,FALSE,"SUM M2";"sum02",#N/A,FALSE,"SUM 02";"sum03",#N/A,FALSE,"SUM 03";"sum04",#N/A,FALSE,"SUM 04";"sum05",#N/A,FALSE,"SUM 05"}</definedName>
-    <definedName name="FaultList1">[6]Selections!$H$2:$H$4</definedName>
+    <definedName name="FaultList1">[5]Selections!$H$2:$H$4</definedName>
     <definedName name="ｆｃ">#REF!</definedName>
     <definedName name="FC_MES_MIX_CON_PROD_PARA_VANESSA">#REF!</definedName>
     <definedName name="fca">#REF!</definedName>
@@ -1306,7 +1305,7 @@
     <definedName name="hdfghfg" localSheetId="0" hidden="1">{"SUM ALL YR",#N/A,FALSE,"SUM ALL YR";"sum01",#N/A,FALSE,"SUM 01";"sumM2",#N/A,FALSE,"SUM M2";"sum02",#N/A,FALSE,"SUM 02";"sum03",#N/A,FALSE,"SUM 03";"sum04",#N/A,FALSE,"SUM 04";"sum05",#N/A,FALSE,"SUM 05"}</definedName>
     <definedName name="hdfghfg" hidden="1">{"SUM ALL YR",#N/A,FALSE,"SUM ALL YR";"sum01",#N/A,FALSE,"SUM 01";"sumM2",#N/A,FALSE,"SUM M2";"sum02",#N/A,FALSE,"SUM 02";"sum03",#N/A,FALSE,"SUM 03";"sum04",#N/A,FALSE,"SUM 04";"sum05",#N/A,FALSE,"SUM 05"}</definedName>
     <definedName name="HEV">#REF!</definedName>
-    <definedName name="Hex_LB">[7]Selections!$A$2:$A$103</definedName>
+    <definedName name="Hex_LB">[6]Selections!$A$2:$A$103</definedName>
     <definedName name="HF1_HARN">#N/A</definedName>
     <definedName name="ｈｇｈｆｇ" localSheetId="0">InpMove5</definedName>
     <definedName name="ｈｇｈｆｇ">InpMove5</definedName>
@@ -1331,8 +1330,8 @@
     <definedName name="I\\\\\\">#REF!</definedName>
     <definedName name="IF">#REF!</definedName>
     <definedName name="II" hidden="1">#REF!</definedName>
-    <definedName name="Implementation" localSheetId="0">[3]Selections!$I$1:$I$2</definedName>
-    <definedName name="Implementation">[4]Selections!$I$1:$I$2</definedName>
+    <definedName name="Implementation" localSheetId="0">[2]Selections!$I$1:$I$2</definedName>
+    <definedName name="Implementation">[3]Selections!$I$1:$I$2</definedName>
     <definedName name="INC">#REF!</definedName>
     <definedName name="INDENT">#N/A</definedName>
     <definedName name="InterProductManage">#REF!</definedName>
@@ -1506,8 +1505,8 @@
     <definedName name="MCXvar">#REF!</definedName>
     <definedName name="MDL">#REF!</definedName>
     <definedName name="MDLYR">#REF!</definedName>
-    <definedName name="Memory" localSheetId="0">[3]Selections!$G$1:$G$4</definedName>
-    <definedName name="Memory">[4]Selections!$G$1:$G$4</definedName>
+    <definedName name="Memory" localSheetId="0">[2]Selections!$G$1:$G$4</definedName>
+    <definedName name="Memory">[3]Selections!$G$1:$G$4</definedName>
     <definedName name="Memphis_a">#REF!</definedName>
     <definedName name="MENU">#REF!</definedName>
     <definedName name="MENU1">#REF!</definedName>
@@ -1544,9 +1543,9 @@
     <definedName name="month3_direct">#REF!</definedName>
     <definedName name="month3_lease">#REF!</definedName>
     <definedName name="MOTO">#REF!</definedName>
-    <definedName name="MSB_LSB" localSheetId="0">[3]Selections!$B$1:$B$3</definedName>
-    <definedName name="MSB_LSB">[4]Selections!$B$1:$B$3</definedName>
-    <definedName name="MSB_LSB_List">[8]Selections!$B$1:$B$3</definedName>
+    <definedName name="MSB_LSB" localSheetId="0">[2]Selections!$B$1:$B$3</definedName>
+    <definedName name="MSB_LSB">[3]Selections!$B$1:$B$3</definedName>
+    <definedName name="MSB_LSB_List">[7]Selections!$B$1:$B$3</definedName>
     <definedName name="MSRP">#REF!</definedName>
     <definedName name="MSRP95">#REF!</definedName>
     <definedName name="MSRP96">#REF!</definedName>
@@ -1595,8 +1594,8 @@
     <definedName name="NNN">#REF!</definedName>
     <definedName name="no" localSheetId="0">#REF!</definedName>
     <definedName name="no">#REF!</definedName>
-    <definedName name="No_Yes" localSheetId="0">[3]Selections!$A$1:$A$3</definedName>
-    <definedName name="No_Yes">[4]Selections!$A$1:$A$3</definedName>
+    <definedName name="No_Yes" localSheetId="0">[2]Selections!$A$1:$A$3</definedName>
+    <definedName name="No_Yes">[3]Selections!$A$1:$A$3</definedName>
     <definedName name="Noff">#REF!</definedName>
     <definedName name="Ｎｏｓ">#REF!</definedName>
     <definedName name="Ｎｏｕｔ">#REF!</definedName>
@@ -1642,20 +1641,20 @@
     <definedName name="P_2">#REF!</definedName>
     <definedName name="P_3">#REF!</definedName>
     <definedName name="P_IMｸﾞﾗﾌ">#REF!</definedName>
-    <definedName name="P2_DIDs" localSheetId="0">[9]Ref_Ranges!$AI$2:$AI$3</definedName>
-    <definedName name="P2_DIDs">[10]Ref_Ranges!$AI$2:$AI$3</definedName>
-    <definedName name="P2_ECUPins" localSheetId="0">OFFSET([11]Ref_Ranges!$N$1,1,0,IF(MATCH("*",[11]Ref_Ranges!$N:$N,-1)&gt;2,MATCH("*",[11]Ref_Ranges!$N:$N,-1),3)-1,1)</definedName>
-    <definedName name="P2_ECUPins">OFFSET([12]Ref_Ranges!$N$1,1,0,IF(MATCH("*",[12]Ref_Ranges!$N:$N,-1)&gt;2,MATCH("*",[12]Ref_Ranges!$N:$N,-1),3)-1,1)</definedName>
-    <definedName name="P2_ECUType" localSheetId="0">[9]Header!$D$139:$D$150</definedName>
-    <definedName name="P2_ECUType">[10]Header!$D$139:$D$150</definedName>
-    <definedName name="P2_ExtDataList" localSheetId="0">[9]Ref_Ranges!$AE$2:$AE$4</definedName>
-    <definedName name="P2_ExtDataList">[10]Ref_Ranges!$AE$2:$AE$4</definedName>
-    <definedName name="P2_LSDIDList" localSheetId="0">[9]Ref_Ranges!$X$2:$X$4</definedName>
-    <definedName name="P2_LSDIDList">[10]Ref_Ranges!$X$2:$X$4</definedName>
-    <definedName name="P2_SSD3SymtomValidator" localSheetId="0">[9]Ref_Ranges!$AK$2:$AK$3</definedName>
-    <definedName name="P2_SSD3SymtomValidator">[10]Ref_Ranges!$AK$2:$AK$3</definedName>
-    <definedName name="P2_Symptom_Validator" localSheetId="0">OFFSET([9]Ref_Ranges!$P$1,1,0,IF(MATCH("*",[9]Ref_Ranges!$P:$P,-1)&gt;2,MATCH("*",[9]Ref_Ranges!$P:$P,-1),3)-1,1)</definedName>
-    <definedName name="P2_Symptom_Validator">OFFSET([10]Ref_Ranges!$P$1,1,0,IF(MATCH("*",[10]Ref_Ranges!$P:$P,-1)&gt;2,MATCH("*",[10]Ref_Ranges!$P:$P,-1),3)-1,1)</definedName>
+    <definedName name="P2_DIDs" localSheetId="0">[8]Ref_Ranges!$AI$2:$AI$3</definedName>
+    <definedName name="P2_DIDs">[9]Ref_Ranges!$AI$2:$AI$3</definedName>
+    <definedName name="P2_ECUPins" localSheetId="0">OFFSET([10]Ref_Ranges!$N$1,1,0,IF(MATCH("*",[10]Ref_Ranges!$N:$N,-1)&gt;2,MATCH("*",[10]Ref_Ranges!$N:$N,-1),3)-1,1)</definedName>
+    <definedName name="P2_ECUPins">OFFSET([11]Ref_Ranges!$N$1,1,0,IF(MATCH("*",[11]Ref_Ranges!$N:$N,-1)&gt;2,MATCH("*",[11]Ref_Ranges!$N:$N,-1),3)-1,1)</definedName>
+    <definedName name="P2_ECUType" localSheetId="0">[8]Header!$D$139:$D$150</definedName>
+    <definedName name="P2_ECUType">[9]Header!$D$139:$D$150</definedName>
+    <definedName name="P2_ExtDataList" localSheetId="0">[8]Ref_Ranges!$AE$2:$AE$4</definedName>
+    <definedName name="P2_ExtDataList">[9]Ref_Ranges!$AE$2:$AE$4</definedName>
+    <definedName name="P2_LSDIDList" localSheetId="0">[8]Ref_Ranges!$X$2:$X$4</definedName>
+    <definedName name="P2_LSDIDList">[9]Ref_Ranges!$X$2:$X$4</definedName>
+    <definedName name="P2_SSD3SymtomValidator" localSheetId="0">[8]Ref_Ranges!$AK$2:$AK$3</definedName>
+    <definedName name="P2_SSD3SymtomValidator">[9]Ref_Ranges!$AK$2:$AK$3</definedName>
+    <definedName name="P2_Symptom_Validator" localSheetId="0">OFFSET([8]Ref_Ranges!$P$1,1,0,IF(MATCH("*",[8]Ref_Ranges!$P:$P,-1)&gt;2,MATCH("*",[8]Ref_Ranges!$P:$P,-1),3)-1,1)</definedName>
+    <definedName name="P2_Symptom_Validator">OFFSET([9]Ref_Ranges!$P$1,1,0,IF(MATCH("*",[9]Ref_Ranges!$P:$P,-1)&gt;2,MATCH("*",[9]Ref_Ranges!$P:$P,-1),3)-1,1)</definedName>
     <definedName name="P6改" localSheetId="0" hidden="1">{"SUM ALL YR",#N/A,FALSE,"SUM ALL YR";"sum01",#N/A,FALSE,"SUM 01";"sumM2",#N/A,FALSE,"SUM M2";"sum02",#N/A,FALSE,"SUM 02";"sum03",#N/A,FALSE,"SUM 03";"sum04",#N/A,FALSE,"SUM 04";"sum05",#N/A,FALSE,"SUM 05"}</definedName>
     <definedName name="P6改" hidden="1">{"SUM ALL YR",#N/A,FALSE,"SUM ALL YR";"sum01",#N/A,FALSE,"SUM 01";"sumM2",#N/A,FALSE,"SUM M2";"sum02",#N/A,FALSE,"SUM 02";"sum03",#N/A,FALSE,"SUM 03";"sum04",#N/A,FALSE,"SUM 04";"sum05",#N/A,FALSE,"SUM 05"}</definedName>
     <definedName name="PACOST">#REF!</definedName>
@@ -1676,7 +1675,7 @@
     <definedName name="PATEXT">#REF!</definedName>
     <definedName name="Payment_24">#REF!</definedName>
     <definedName name="Payment_36">#REF!</definedName>
-    <definedName name="PBCU_Codes">[2]Selections!$D$2:$D$5</definedName>
+    <definedName name="PBCU_Codes">[1]Selections!$D$2:$D$5</definedName>
     <definedName name="PCAT">#REF!</definedName>
     <definedName name="PDSPEC">#REF!</definedName>
     <definedName name="PenRate">#REF!</definedName>
@@ -1737,7 +1736,7 @@
     <definedName name="PRINTSCOST">#REF!</definedName>
     <definedName name="PRINTVA">#REF!</definedName>
     <definedName name="PRINTW">#REF!</definedName>
-    <definedName name="Priority">[2]Selections!$I$2:$I$6</definedName>
+    <definedName name="Priority">[1]Selections!$I$2:$I$6</definedName>
     <definedName name="Prix">#REF!</definedName>
     <definedName name="PRT">#REF!</definedName>
     <definedName name="PSCOST">#REF!</definedName>
@@ -1772,8 +1771,8 @@
     <definedName name="QX4PR">#REF!</definedName>
     <definedName name="Q従業員名簿ｴｸｽﾎﾟｰﾄ用">#REF!</definedName>
     <definedName name="R_FLUSH_B1..M10">#REF!</definedName>
-    <definedName name="R_IO_W" localSheetId="0">[3]Selections!$D$1:$D$9</definedName>
-    <definedName name="R_IO_W">[4]Selections!$D$1:$D$9</definedName>
+    <definedName name="R_IO_W" localSheetId="0">[2]Selections!$D$1:$D$9</definedName>
+    <definedName name="R_IO_W">[3]Selections!$D$1:$D$9</definedName>
     <definedName name="RANGE">#REF!</definedName>
     <definedName name="RANGE1">#REF!</definedName>
     <definedName name="rango">#REF!</definedName>
@@ -1789,8 +1788,8 @@
     <definedName name="repurch_alamo">#REF!</definedName>
     <definedName name="repurch_base">#REF!</definedName>
     <definedName name="repurch_enter">#REF!</definedName>
-    <definedName name="Req_5" localSheetId="0">'[13]1.General'!#REF!</definedName>
-    <definedName name="Req_5">'[14]1.general'!#REF!</definedName>
+    <definedName name="Req_5" localSheetId="0">'[12]1.General'!#REF!</definedName>
+    <definedName name="Req_5">'[13]1.general'!#REF!</definedName>
     <definedName name="RES__24">#REF!</definedName>
     <definedName name="RES__36">#REF!</definedName>
     <definedName name="residual_support">#REF!</definedName>
@@ -1843,8 +1842,8 @@
     <definedName name="ｒてれ">ｇｇｇｒ</definedName>
     <definedName name="ｒふぇえ" localSheetId="0">InpMove6</definedName>
     <definedName name="ｒふぇえ">InpMove6</definedName>
-    <definedName name="s" localSheetId="0">[15]Selections!$I$2:$I$6</definedName>
-    <definedName name="s">[16]Selections!$I$2:$I$6</definedName>
+    <definedName name="s" localSheetId="0">[14]Selections!$I$2:$I$6</definedName>
+    <definedName name="s">[15]Selections!$I$2:$I$6</definedName>
     <definedName name="S\">#REF!</definedName>
     <definedName name="S\\">#REF!</definedName>
     <definedName name="S\\\">#REF!</definedName>
@@ -1874,8 +1873,8 @@
     <definedName name="ｓｄｓｗｗ">InpMove12</definedName>
     <definedName name="ｓｄふぁｓｆだｓｄふぁｓｆあせｆあｓｆだｓ">#REF!</definedName>
     <definedName name="se">#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!</definedName>
-    <definedName name="Security_Required" localSheetId="0">[3]Selections!$H$1:$H$3</definedName>
-    <definedName name="Security_Required">[4]Selections!$H$1:$H$3</definedName>
+    <definedName name="Security_Required" localSheetId="0">[2]Selections!$H$1:$H$3</definedName>
+    <definedName name="Security_Required">[3]Selections!$H$1:$H$3</definedName>
     <definedName name="Segment_Sales">#REF!</definedName>
     <definedName name="segment_share">#REF!</definedName>
     <definedName name="SEINO">#REF!</definedName>
@@ -1939,7 +1938,7 @@
     <definedName name="temp">#REF!</definedName>
     <definedName name="TEST">#REF!</definedName>
     <definedName name="text">#REF!</definedName>
-    <definedName name="Text_LB">[2]Selections!$B$2:$B$103</definedName>
+    <definedName name="Text_LB">[1]Selections!$B$2:$B$103</definedName>
     <definedName name="texy">#REF!</definedName>
     <definedName name="ｔｇで" localSheetId="0">TMdatadisp1</definedName>
     <definedName name="ｔｇで">TMdatadisp1</definedName>
@@ -2177,8 +2176,8 @@
     <definedName name="ｘ81ｂ01">'CDS Coding'!ｘ81ｂ01</definedName>
     <definedName name="XX" localSheetId="0">#N/A</definedName>
     <definedName name="XX">'CDS Coding'!XX</definedName>
-    <definedName name="xxa1">[17]DataBlock!#REF!</definedName>
-    <definedName name="xxx1">[17]DataBlock!#REF!</definedName>
+    <definedName name="xxa1">[16]DataBlock!#REF!</definedName>
+    <definedName name="xxx1">[16]DataBlock!#REF!</definedName>
     <definedName name="Y">#N/A</definedName>
     <definedName name="Y\">#REF!</definedName>
     <definedName name="Y\\">#REF!</definedName>
@@ -2186,12 +2185,12 @@
     <definedName name="Y\\\\">#REF!</definedName>
     <definedName name="Y\\\\\">#REF!</definedName>
     <definedName name="Y\\\\\\">#REF!</definedName>
-    <definedName name="yaa1">[17]DataBlock!#REF!</definedName>
+    <definedName name="yaa1">[16]DataBlock!#REF!</definedName>
     <definedName name="yes" localSheetId="0">#REF!</definedName>
     <definedName name="yes">#REF!</definedName>
-    <definedName name="yes_no">[2]Selections!$E$2:$E$3</definedName>
+    <definedName name="yes_no">[1]Selections!$E$2:$E$3</definedName>
     <definedName name="ｙｙｒｔ">#N/A</definedName>
-    <definedName name="yyy1">[17]DataBlock!#REF!</definedName>
+    <definedName name="yyy1">[16]DataBlock!#REF!</definedName>
     <definedName name="z" localSheetId="0" hidden="1">{"RESUMEN",#N/A,FALSE,"BASE ANEXOS";"ANEXO 1",#N/A,FALSE,"BASE ANEXOS";"ANEXO 2",#N/A,FALSE,"BASE ANEXOS"}</definedName>
     <definedName name="z" hidden="1">{"RESUMEN",#N/A,FALSE,"BASE ANEXOS";"ANEXO 1",#N/A,FALSE,"BASE ANEXOS";"ANEXO 2",#N/A,FALSE,"BASE ANEXOS"}</definedName>
     <definedName name="Z\">#REF!</definedName>
@@ -2216,7 +2215,7 @@
     <definedName name="Ｚｐｓ">#REF!</definedName>
     <definedName name="Ｚｓ">#REF!</definedName>
     <definedName name="ZZ" hidden="1">#REF!</definedName>
-    <definedName name="zzz1">[17]DataBlock!#REF!</definedName>
+    <definedName name="zzz1">[16]DataBlock!#REF!</definedName>
     <definedName name="α">#REF!</definedName>
     <definedName name="αf">#REF!</definedName>
     <definedName name="αm">#REF!</definedName>
@@ -2461,21 +2460,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="64">
   <si>
-    <t>Parameter</t>
-  </si>
-  <si>
-    <t>BytePos (from 0)</t>
-  </si>
-  <si>
-    <t>BitPos</t>
-  </si>
-  <si>
-    <t>BitLength</t>
-  </si>
-  <si>
-    <t>MethodType</t>
-  </si>
-  <si>
     <t>Format Byte</t>
   </si>
   <si>
@@ -2859,6 +2843,21 @@
 0xC=  TOP
 0xD= Heriogreen
 0xFF=Invalid</t>
+  </si>
+  <si>
+    <t>$Parameter</t>
+  </si>
+  <si>
+    <t>$BytePos (from 0)</t>
+  </si>
+  <si>
+    <t>$BitPos</t>
+  </si>
+  <si>
+    <t>$BitLength</t>
+  </si>
+  <si>
+    <t>$MethodType</t>
   </si>
 </sst>
 </file>
@@ -3298,56 +3297,33 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Document Regulation"/>
-      <sheetName val="Change Log &amp; General Info"/>
-      <sheetName val="Diagnostics Services"/>
-      <sheetName val="System DID"/>
-      <sheetName val="ECU DID"/>
-      <sheetName val="DTC-List"/>
-      <sheetName val="FTB_RepairAction Refer"/>
-      <sheetName val="ECU Component data sheet"/>
-      <sheetName val="Snapshot DIDs"/>
-      <sheetName val="Extended Data"/>
-      <sheetName val="Routines Data (0x31)"/>
-      <sheetName val="Basic DIDs Check"/>
-      <sheetName val="Write VIN"/>
-      <sheetName val="initialization"/>
-      <sheetName val="ECU Exchange"/>
-      <sheetName val="CDS Coding"/>
-      <sheetName val="Flashing Sequence"/>
-      <sheetName val="VOD Coding"/>
-      <sheetName val="IO Control (2F)"/>
-      <sheetName val="Calibration Sequence"/>
-      <sheetName val="VF5NP EDR"/>
-      <sheetName val="Read EDR Sequence"/>
+      <sheetName val="Overview"/>
+      <sheetName val="Change History"/>
+      <sheetName val="Fault List"/>
+      <sheetName val="Terms and Acronyms"/>
+      <sheetName val="Fauth_List_Future"/>
+      <sheetName val="Selections"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet2"/>
+      <sheetName val="Notes"/>
+      <sheetName val="SelfTestDTC"/>
+      <sheetName val="DTC Guidelines"/>
+      <sheetName val="PDU"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
       <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3466,6 +3442,10 @@
       <sheetName val="Events"/>
       <sheetName val="Ref_DSVars"/>
       <sheetName val="Ref_SecurityLevels"/>
+      <sheetName val="DiagRoutine (0E00)"/>
+      <sheetName val="DiagRoutine (0E12)"/>
+      <sheetName val="DiagRoutine (0E13)"/>
+      <sheetName val="DiagRoutine (0E01)"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -3577,6 +3557,10 @@
       <sheetData sheetId="106"/>
       <sheetData sheetId="107"/>
       <sheetData sheetId="108"/>
+      <sheetData sheetId="109"/>
+      <sheetData sheetId="110"/>
+      <sheetData sheetId="111"/>
+      <sheetData sheetId="112" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3823,243 +3807,6 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
-      <sheetName val="Header"/>
-      <sheetName val="Network Config"/>
-      <sheetName val="Change Details"/>
-      <sheetName val="Detail Review Record (1)"/>
-      <sheetName val="Detail Review Record (2)"/>
-      <sheetName val="Detail Review Record (3)"/>
-      <sheetName val="Detail Review Record (4)"/>
-      <sheetName val="Detail Review Record (5)"/>
-      <sheetName val="Detail Review Record (6)"/>
-      <sheetName val="Detail Review Record (7)"/>
-      <sheetName val="Detail Review Record (8)"/>
-      <sheetName val="Detail Review Record (9)"/>
-      <sheetName val="Detail Review Record (10)"/>
-      <sheetName val="Detail Review Record (11)"/>
-      <sheetName val="Issues List"/>
-      <sheetName val="Contents"/>
-      <sheetName val="Diagnostic Services"/>
-      <sheetName val="Diag Sessions and Security"/>
-      <sheetName val="DiagRoutine(1)"/>
-      <sheetName val="DiagRoutine(2)"/>
-      <sheetName val="DiagRoutine(6)"/>
-      <sheetName val="DiagRoutine(3)"/>
-      <sheetName val="DiagRoutine(4)"/>
-      <sheetName val="DiagRoutine(8)"/>
-      <sheetName val="DiagRoutine(9)"/>
-      <sheetName val="DiagRoutine(5)"/>
-      <sheetName val="DiagRoutine(7)"/>
-      <sheetName val="DiagRoutine(10)"/>
-      <sheetName val="R W Data By ID (Unsigned Num)"/>
-      <sheetName val="R W Data By ID (Signed Num)"/>
-      <sheetName val="R W Data By ID (ASCII)"/>
-      <sheetName val="R W Data By ID (HEX)"/>
-      <sheetName val="R W Data By ID (BCD)"/>
-      <sheetName val="R W Data By ID (SED)"/>
-      <sheetName val="R W Data By ID (BFP)"/>
-      <sheetName val="R W Data By ID (BM)"/>
-      <sheetName val="R W Data By ID (PKT)"/>
-      <sheetName val="IO Ctrl By ID (Unsigned)"/>
-      <sheetName val="IO Ctrl By ID (Signed)"/>
-      <sheetName val="IO Ctrl By ID (HEX)"/>
-      <sheetName val="IO Ctrl By ID (BCD)"/>
-      <sheetName val="IO Ctrl By ID (SED)"/>
-      <sheetName val="IO Ctrl By ID (BFP)"/>
-      <sheetName val="IO Ctrl By ID (BM)"/>
-      <sheetName val="IO Ctrl By ID (PKT)"/>
-      <sheetName val="DynamicallyDefineDataId"/>
-      <sheetName val="ReadDataByPeriodicId"/>
-      <sheetName val="Read Memory By Address"/>
-      <sheetName val="Write Memory By Address"/>
-      <sheetName val="ListNumberOfDIDs"/>
-      <sheetName val="ECUDTCs"/>
-      <sheetName val="Master List of DTCs"/>
-      <sheetName val="DTC Snapshot Data IDs"/>
-      <sheetName val="DTC Extended Data IDs"/>
-      <sheetName val="Fault Setting-Delete Conditions"/>
-      <sheetName val="Boot Loader Services"/>
-      <sheetName val="Routine Identifiers (Boot)"/>
-      <sheetName val="RW Data By ID (Boot)"/>
-      <sheetName val="Data Transfer Upload &amp; Download"/>
-      <sheetName val="MasterConfigData-T5"/>
-      <sheetName val="MasterConfigData-EUCD"/>
-      <sheetName val="MasterMultiCANData"/>
-      <sheetName val="Module Set up Requirements"/>
-      <sheetName val="Overview"/>
-      <sheetName val="Module Connector Info"/>
-      <sheetName val="Notes"/>
-      <sheetName val="Non Compliance"/>
-      <sheetName val="OBDService1"/>
-      <sheetName val="OBDService2"/>
-      <sheetName val="OBDService6"/>
-      <sheetName val="OBDService9"/>
-      <sheetName val="OBDServices"/>
-      <sheetName val="SecurityConstants"/>
-      <sheetName val="Form Use Notes"/>
-      <sheetName val="Ref_ECU"/>
-      <sheetName val="Ref_DTC"/>
-      <sheetName val="Ref_DTCFaults"/>
-      <sheetName val="Ref_PIDMasterList"/>
-      <sheetName val="Ref_PIDUnsignedNumeric"/>
-      <sheetName val="Ref_PIDSignedNumeric"/>
-      <sheetName val="Ref_PIDStateEncoded"/>
-      <sheetName val="Ref_PIDBitMapped"/>
-      <sheetName val="Ref_PIDPacketed"/>
-      <sheetName val="Ref_PIDBinaryFloat"/>
-      <sheetName val="Ref_Routine_Master_List"/>
-      <sheetName val="Ref_T5"/>
-      <sheetName val="Ref_Units"/>
-      <sheetName val="Ref_EUCD"/>
-      <sheetName val="Ref_MultiCAN"/>
-      <sheetName val="Ref_Models"/>
-      <sheetName val="Ref_ISOTestIds"/>
-      <sheetName val="Ref_ScalingIds"/>
-      <sheetName val="Checks"/>
-      <sheetName val="Ref_FlexRayAndDoIP_IDs"/>
-      <sheetName val="Ref_EOL"/>
-      <sheetName val="Generic PID's"/>
-      <sheetName val="Generic Routines"/>
-      <sheetName val="Generic DTC's"/>
-      <sheetName val="Extracts"/>
-      <sheetName val="Import"/>
-      <sheetName val="Help"/>
-      <sheetName val="DiagRoutine"/>
-      <sheetName val="About"/>
-      <sheetName val="Maintenance"/>
-      <sheetName val="Detail Review Record"/>
-      <sheetName val="Ref_Ranges"/>
-      <sheetName val="Events"/>
-      <sheetName val="Ref_DSVars"/>
-      <sheetName val="Ref_SecurityLevels"/>
-      <sheetName val="DiagRoutine (0E00)"/>
-      <sheetName val="DiagRoutine (0E12)"/>
-      <sheetName val="DiagRoutine (0E13)"/>
-      <sheetName val="DiagRoutine (0E01)"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
-      <sheetData sheetId="28"/>
-      <sheetData sheetId="29"/>
-      <sheetData sheetId="30"/>
-      <sheetData sheetId="31"/>
-      <sheetData sheetId="32"/>
-      <sheetData sheetId="33"/>
-      <sheetData sheetId="34"/>
-      <sheetData sheetId="35"/>
-      <sheetData sheetId="36"/>
-      <sheetData sheetId="37"/>
-      <sheetData sheetId="38"/>
-      <sheetData sheetId="39"/>
-      <sheetData sheetId="40"/>
-      <sheetData sheetId="41"/>
-      <sheetData sheetId="42"/>
-      <sheetData sheetId="43"/>
-      <sheetData sheetId="44"/>
-      <sheetData sheetId="45"/>
-      <sheetData sheetId="46"/>
-      <sheetData sheetId="47"/>
-      <sheetData sheetId="48"/>
-      <sheetData sheetId="49"/>
-      <sheetData sheetId="50"/>
-      <sheetData sheetId="51"/>
-      <sheetData sheetId="52"/>
-      <sheetData sheetId="53"/>
-      <sheetData sheetId="54"/>
-      <sheetData sheetId="55"/>
-      <sheetData sheetId="56"/>
-      <sheetData sheetId="57"/>
-      <sheetData sheetId="58"/>
-      <sheetData sheetId="59"/>
-      <sheetData sheetId="60"/>
-      <sheetData sheetId="61"/>
-      <sheetData sheetId="62"/>
-      <sheetData sheetId="63"/>
-      <sheetData sheetId="64"/>
-      <sheetData sheetId="65"/>
-      <sheetData sheetId="66"/>
-      <sheetData sheetId="67"/>
-      <sheetData sheetId="68"/>
-      <sheetData sheetId="69"/>
-      <sheetData sheetId="70"/>
-      <sheetData sheetId="71"/>
-      <sheetData sheetId="72"/>
-      <sheetData sheetId="73"/>
-      <sheetData sheetId="74"/>
-      <sheetData sheetId="75"/>
-      <sheetData sheetId="76"/>
-      <sheetData sheetId="77"/>
-      <sheetData sheetId="78"/>
-      <sheetData sheetId="79"/>
-      <sheetData sheetId="80"/>
-      <sheetData sheetId="81"/>
-      <sheetData sheetId="82"/>
-      <sheetData sheetId="83"/>
-      <sheetData sheetId="84"/>
-      <sheetData sheetId="85"/>
-      <sheetData sheetId="86"/>
-      <sheetData sheetId="87"/>
-      <sheetData sheetId="88"/>
-      <sheetData sheetId="89"/>
-      <sheetData sheetId="90"/>
-      <sheetData sheetId="91"/>
-      <sheetData sheetId="92"/>
-      <sheetData sheetId="93"/>
-      <sheetData sheetId="94"/>
-      <sheetData sheetId="95"/>
-      <sheetData sheetId="96"/>
-      <sheetData sheetId="97"/>
-      <sheetData sheetId="98"/>
-      <sheetData sheetId="99"/>
-      <sheetData sheetId="100"/>
-      <sheetData sheetId="101"/>
-      <sheetData sheetId="102"/>
-      <sheetData sheetId="103"/>
-      <sheetData sheetId="104"/>
-      <sheetData sheetId="105"/>
-      <sheetData sheetId="106"/>
-      <sheetData sheetId="107"/>
-      <sheetData sheetId="108"/>
-      <sheetData sheetId="109"/>
-      <sheetData sheetId="110"/>
-      <sheetData sheetId="111"/>
-      <sheetData sheetId="112" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
       <sheetName val="Macro1"/>
       <sheetName val="封面"/>
       <sheetName val="RevisionRecords"/>
@@ -4103,7 +3850,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4128,7 +3875,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4193,7 +3940,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4252,7 +3999,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4321,32 +4068,14 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
-      <sheetName val="Overview"/>
-      <sheetName val="Change History"/>
-      <sheetName val="Fault List"/>
-      <sheetName val="Terms and Acronyms"/>
-      <sheetName val="Fauth_List_Future"/>
+      <sheetName val="VF31 REQ External Discussion"/>
+      <sheetName val="VFe34_GauTui_Requirement_Discus"/>
       <sheetName val="Selections"/>
-      <sheetName val="Sheet1"/>
-      <sheetName val="Sheet2"/>
-      <sheetName val="Notes"/>
-      <sheetName val="SelfTestDTC"/>
-      <sheetName val="DTC Guidelines"/>
-      <sheetName val="PDU"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4390,23 +4119,6 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
-      <sheetName val="VF31 REQ External Discussion"/>
-      <sheetName val="VFe34_GauTui_Requirement_Discus"/>
-      <sheetName val="Selections"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
       <sheetName val="Overview"/>
       <sheetName val="Change History"/>
       <sheetName val="Terms and Acronyms"/>
@@ -4432,7 +4144,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4469,7 +4181,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4510,7 +4222,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4736,6 +4448,235 @@
       <sheetData sheetId="107"/>
       <sheetData sheetId="108"/>
       <sheetData sheetId="109" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Header"/>
+      <sheetName val="Network Config"/>
+      <sheetName val="Change Details"/>
+      <sheetName val="Detail Review Record (1)"/>
+      <sheetName val="Detail Review Record (2)"/>
+      <sheetName val="Detail Review Record (3)"/>
+      <sheetName val="Detail Review Record (4)"/>
+      <sheetName val="Detail Review Record (5)"/>
+      <sheetName val="Detail Review Record (6)"/>
+      <sheetName val="Detail Review Record (7)"/>
+      <sheetName val="Detail Review Record (8)"/>
+      <sheetName val="Detail Review Record (9)"/>
+      <sheetName val="Detail Review Record (10)"/>
+      <sheetName val="Detail Review Record (11)"/>
+      <sheetName val="Issues List"/>
+      <sheetName val="Contents"/>
+      <sheetName val="Diagnostic Services"/>
+      <sheetName val="Diag Sessions and Security"/>
+      <sheetName val="DiagRoutine(1)"/>
+      <sheetName val="DiagRoutine(2)"/>
+      <sheetName val="DiagRoutine(6)"/>
+      <sheetName val="DiagRoutine(3)"/>
+      <sheetName val="DiagRoutine(4)"/>
+      <sheetName val="DiagRoutine(8)"/>
+      <sheetName val="DiagRoutine(9)"/>
+      <sheetName val="DiagRoutine(5)"/>
+      <sheetName val="DiagRoutine(7)"/>
+      <sheetName val="DiagRoutine(10)"/>
+      <sheetName val="R W Data By ID (Unsigned Num)"/>
+      <sheetName val="R W Data By ID (Signed Num)"/>
+      <sheetName val="R W Data By ID (ASCII)"/>
+      <sheetName val="R W Data By ID (HEX)"/>
+      <sheetName val="R W Data By ID (BCD)"/>
+      <sheetName val="R W Data By ID (SED)"/>
+      <sheetName val="R W Data By ID (BFP)"/>
+      <sheetName val="R W Data By ID (BM)"/>
+      <sheetName val="R W Data By ID (PKT)"/>
+      <sheetName val="IO Ctrl By ID (Unsigned)"/>
+      <sheetName val="IO Ctrl By ID (Signed)"/>
+      <sheetName val="IO Ctrl By ID (HEX)"/>
+      <sheetName val="IO Ctrl By ID (BCD)"/>
+      <sheetName val="IO Ctrl By ID (SED)"/>
+      <sheetName val="IO Ctrl By ID (BFP)"/>
+      <sheetName val="IO Ctrl By ID (BM)"/>
+      <sheetName val="IO Ctrl By ID (PKT)"/>
+      <sheetName val="DynamicallyDefineDataId"/>
+      <sheetName val="ReadDataByPeriodicId"/>
+      <sheetName val="Read Memory By Address"/>
+      <sheetName val="Write Memory By Address"/>
+      <sheetName val="ListNumberOfDIDs"/>
+      <sheetName val="ECUDTCs"/>
+      <sheetName val="Master List of DTCs"/>
+      <sheetName val="DTC Snapshot Data IDs"/>
+      <sheetName val="DTC Extended Data IDs"/>
+      <sheetName val="Fault Setting-Delete Conditions"/>
+      <sheetName val="Boot Loader Services"/>
+      <sheetName val="Routine Identifiers (Boot)"/>
+      <sheetName val="RW Data By ID (Boot)"/>
+      <sheetName val="Data Transfer Upload &amp; Download"/>
+      <sheetName val="MasterConfigData-T5"/>
+      <sheetName val="MasterConfigData-EUCD"/>
+      <sheetName val="MasterMultiCANData"/>
+      <sheetName val="Module Set up Requirements"/>
+      <sheetName val="Overview"/>
+      <sheetName val="Module Connector Info"/>
+      <sheetName val="Notes"/>
+      <sheetName val="Non Compliance"/>
+      <sheetName val="OBDService1"/>
+      <sheetName val="OBDService2"/>
+      <sheetName val="OBDService6"/>
+      <sheetName val="OBDService9"/>
+      <sheetName val="OBDServices"/>
+      <sheetName val="SecurityConstants"/>
+      <sheetName val="Form Use Notes"/>
+      <sheetName val="Ref_ECU"/>
+      <sheetName val="Ref_DTC"/>
+      <sheetName val="Ref_DTCFaults"/>
+      <sheetName val="Ref_PIDMasterList"/>
+      <sheetName val="Ref_PIDUnsignedNumeric"/>
+      <sheetName val="Ref_PIDSignedNumeric"/>
+      <sheetName val="Ref_PIDStateEncoded"/>
+      <sheetName val="Ref_PIDBitMapped"/>
+      <sheetName val="Ref_PIDPacketed"/>
+      <sheetName val="Ref_PIDBinaryFloat"/>
+      <sheetName val="Ref_Routine_Master_List"/>
+      <sheetName val="Ref_T5"/>
+      <sheetName val="Ref_Units"/>
+      <sheetName val="Ref_EUCD"/>
+      <sheetName val="Ref_MultiCAN"/>
+      <sheetName val="Ref_Models"/>
+      <sheetName val="Ref_ISOTestIds"/>
+      <sheetName val="Ref_ScalingIds"/>
+      <sheetName val="Checks"/>
+      <sheetName val="Ref_FlexRayAndDoIP_IDs"/>
+      <sheetName val="Ref_EOL"/>
+      <sheetName val="Generic PID's"/>
+      <sheetName val="Generic Routines"/>
+      <sheetName val="Generic DTC's"/>
+      <sheetName val="Extracts"/>
+      <sheetName val="Import"/>
+      <sheetName val="Help"/>
+      <sheetName val="DiagRoutine"/>
+      <sheetName val="About"/>
+      <sheetName val="Maintenance"/>
+      <sheetName val="Detail Review Record"/>
+      <sheetName val="Ref_Ranges"/>
+      <sheetName val="Events"/>
+      <sheetName val="Ref_DSVars"/>
+      <sheetName val="Ref_SecurityLevels"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+      <sheetData sheetId="30"/>
+      <sheetData sheetId="31"/>
+      <sheetData sheetId="32"/>
+      <sheetData sheetId="33"/>
+      <sheetData sheetId="34"/>
+      <sheetData sheetId="35"/>
+      <sheetData sheetId="36"/>
+      <sheetData sheetId="37"/>
+      <sheetData sheetId="38"/>
+      <sheetData sheetId="39"/>
+      <sheetData sheetId="40"/>
+      <sheetData sheetId="41"/>
+      <sheetData sheetId="42"/>
+      <sheetData sheetId="43"/>
+      <sheetData sheetId="44"/>
+      <sheetData sheetId="45"/>
+      <sheetData sheetId="46"/>
+      <sheetData sheetId="47"/>
+      <sheetData sheetId="48"/>
+      <sheetData sheetId="49"/>
+      <sheetData sheetId="50"/>
+      <sheetData sheetId="51"/>
+      <sheetData sheetId="52"/>
+      <sheetData sheetId="53"/>
+      <sheetData sheetId="54"/>
+      <sheetData sheetId="55"/>
+      <sheetData sheetId="56"/>
+      <sheetData sheetId="57"/>
+      <sheetData sheetId="58"/>
+      <sheetData sheetId="59"/>
+      <sheetData sheetId="60"/>
+      <sheetData sheetId="61"/>
+      <sheetData sheetId="62"/>
+      <sheetData sheetId="63"/>
+      <sheetData sheetId="64"/>
+      <sheetData sheetId="65"/>
+      <sheetData sheetId="66"/>
+      <sheetData sheetId="67"/>
+      <sheetData sheetId="68"/>
+      <sheetData sheetId="69"/>
+      <sheetData sheetId="70"/>
+      <sheetData sheetId="71"/>
+      <sheetData sheetId="72"/>
+      <sheetData sheetId="73"/>
+      <sheetData sheetId="74"/>
+      <sheetData sheetId="75"/>
+      <sheetData sheetId="76"/>
+      <sheetData sheetId="77"/>
+      <sheetData sheetId="78"/>
+      <sheetData sheetId="79"/>
+      <sheetData sheetId="80"/>
+      <sheetData sheetId="81"/>
+      <sheetData sheetId="82"/>
+      <sheetData sheetId="83"/>
+      <sheetData sheetId="84"/>
+      <sheetData sheetId="85"/>
+      <sheetData sheetId="86"/>
+      <sheetData sheetId="87"/>
+      <sheetData sheetId="88"/>
+      <sheetData sheetId="89"/>
+      <sheetData sheetId="90"/>
+      <sheetData sheetId="91"/>
+      <sheetData sheetId="92"/>
+      <sheetData sheetId="93"/>
+      <sheetData sheetId="94"/>
+      <sheetData sheetId="95"/>
+      <sheetData sheetId="96"/>
+      <sheetData sheetId="97"/>
+      <sheetData sheetId="98"/>
+      <sheetData sheetId="99"/>
+      <sheetData sheetId="100"/>
+      <sheetData sheetId="101"/>
+      <sheetData sheetId="102"/>
+      <sheetData sheetId="103"/>
+      <sheetData sheetId="104"/>
+      <sheetData sheetId="105"/>
+      <sheetData sheetId="106"/>
+      <sheetData sheetId="107"/>
+      <sheetData sheetId="108"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5106,24 +5047,24 @@
   <sheetData>
     <row r="1" spans="1:5" s="5" customFormat="1">
       <c r="A1" s="3" t="s">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>4</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="10" customFormat="1">
       <c r="A2" s="6" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B2" s="7">
         <v>3</v>
@@ -5138,7 +5079,7 @@
     </row>
     <row r="3" spans="1:5" s="10" customFormat="1">
       <c r="A3" s="6" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B3" s="8">
         <v>5</v>
@@ -5153,7 +5094,7 @@
     </row>
     <row r="4" spans="1:5" s="15" customFormat="1" ht="216" customHeight="1">
       <c r="A4" s="11" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B4" s="8">
         <v>12</v>
@@ -5165,12 +5106,12 @@
         <v>8</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="15" customFormat="1" ht="347.4" customHeight="1">
       <c r="A5" s="11" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B5" s="8">
         <v>13</v>
@@ -5182,12 +5123,12 @@
         <v>8</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="15" customFormat="1" ht="235.95" customHeight="1">
       <c r="A6" s="11" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B6" s="8">
         <v>14</v>
@@ -5199,12 +5140,12 @@
         <v>8</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="15" customFormat="1" ht="84" customHeight="1">
       <c r="A7" s="11" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B7" s="8">
         <v>15</v>
@@ -5216,12 +5157,12 @@
         <v>4</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="1" customFormat="1" ht="55.2">
       <c r="A8" s="19" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B8" s="8">
         <v>15</v>
@@ -5233,12 +5174,12 @@
         <v>4</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="1" customFormat="1" ht="55.2">
       <c r="A9" s="19" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B9" s="8">
         <v>16</v>
@@ -5250,12 +5191,12 @@
         <v>4</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="15" customFormat="1" ht="82.8">
       <c r="A10" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B10" s="8">
         <v>16</v>
@@ -5267,12 +5208,12 @@
         <v>4</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="15" customFormat="1" ht="82.8">
       <c r="A11" s="11" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B11" s="8">
         <v>17</v>
@@ -5284,12 +5225,12 @@
         <v>4</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="15" customFormat="1" ht="55.2">
       <c r="A12" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B12" s="8">
         <v>17</v>
@@ -5301,12 +5242,12 @@
         <v>4</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="15" customFormat="1" ht="55.2">
       <c r="A13" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B13" s="8">
         <v>18</v>
@@ -5318,12 +5259,12 @@
         <v>4</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="1" customFormat="1" ht="55.2">
       <c r="A14" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B14" s="8">
         <v>18</v>
@@ -5335,12 +5276,12 @@
         <v>4</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="1" customFormat="1" ht="55.2">
       <c r="A15" s="11" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B15" s="8">
         <v>19</v>
@@ -5352,12 +5293,12 @@
         <v>4</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="1" customFormat="1" ht="55.2">
       <c r="A16" s="11" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B16" s="8">
         <v>19</v>
@@ -5369,12 +5310,12 @@
         <v>4</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="1" customFormat="1" ht="55.2">
       <c r="A17" s="11" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B17" s="8">
         <v>20</v>
@@ -5386,12 +5327,12 @@
         <v>4</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="1" customFormat="1" ht="55.2">
       <c r="A18" s="11" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B18" s="8">
         <v>20</v>
@@ -5403,12 +5344,12 @@
         <v>4</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="1" customFormat="1" ht="55.2">
       <c r="A19" s="19" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B19" s="8">
         <v>21</v>
@@ -5420,12 +5361,12 @@
         <v>4</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="1" customFormat="1" ht="55.2">
       <c r="A20" s="6" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B20" s="8">
         <v>21</v>
@@ -5437,12 +5378,12 @@
         <v>4</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="1" customFormat="1" ht="69">
       <c r="A21" s="6" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B21" s="8">
         <v>22</v>
@@ -5454,12 +5395,12 @@
         <v>4</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="1" customFormat="1" ht="69">
       <c r="A22" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B22" s="8">
         <v>22</v>
@@ -5471,12 +5412,12 @@
         <v>4</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="1" customFormat="1" ht="69">
       <c r="A23" s="6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B23" s="8">
         <v>23</v>
@@ -5488,12 +5429,12 @@
         <v>4</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="1" customFormat="1" ht="69">
       <c r="A24" s="6" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B24" s="8">
         <v>23</v>
@@ -5505,12 +5446,12 @@
         <v>4</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:5" s="1" customFormat="1" ht="69">
       <c r="A25" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B25" s="8">
         <v>24</v>
@@ -5522,12 +5463,12 @@
         <v>4</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:5" s="1" customFormat="1" ht="55.2">
       <c r="A26" s="22" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B26" s="8">
         <v>24</v>
@@ -5539,12 +5480,12 @@
         <v>4</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="1" customFormat="1" ht="55.2">
       <c r="A27" s="22" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B27" s="8">
         <v>25</v>
@@ -5556,12 +5497,12 @@
         <v>4</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="1" customFormat="1" ht="55.2">
       <c r="A28" s="6" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B28" s="8">
         <v>25</v>
@@ -5573,12 +5514,12 @@
         <v>4</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:5" s="1" customFormat="1" ht="55.2">
       <c r="A29" s="6" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B29" s="8">
         <v>26</v>
@@ -5590,12 +5531,12 @@
         <v>4</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:5" s="1" customFormat="1" ht="55.2">
       <c r="A30" s="6" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B30" s="8">
         <v>26</v>
@@ -5607,12 +5548,12 @@
         <v>4</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="1:5" s="1" customFormat="1" ht="55.2">
       <c r="A31" s="6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B31" s="8">
         <v>27</v>
@@ -5624,12 +5565,12 @@
         <v>4</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="1" customFormat="1" ht="55.2">
       <c r="A32" s="6" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B32" s="8">
         <v>27</v>
@@ -5641,12 +5582,12 @@
         <v>4</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" spans="1:5" s="1" customFormat="1" ht="55.2">
       <c r="A33" s="6" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B33" s="8">
         <v>28</v>
@@ -5658,12 +5599,12 @@
         <v>4</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="1:5" s="1" customFormat="1" ht="55.2">
       <c r="A34" s="6" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B34" s="8">
         <v>28</v>
@@ -5675,12 +5616,12 @@
         <v>4</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="35" spans="1:5" s="1" customFormat="1" ht="55.2">
       <c r="A35" s="6" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B35" s="8">
         <v>29</v>
@@ -5692,12 +5633,12 @@
         <v>4</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="36" spans="1:5" s="1" customFormat="1" ht="55.2">
       <c r="A36" s="6" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B36" s="8">
         <v>29</v>
@@ -5709,12 +5650,12 @@
         <v>4</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="37" spans="1:5" s="1" customFormat="1" ht="55.2">
       <c r="A37" s="6" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B37" s="8">
         <v>30</v>
@@ -5726,12 +5667,12 @@
         <v>4</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:5" s="1" customFormat="1" ht="55.2">
       <c r="A38" s="6" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B38" s="8">
         <v>30</v>
@@ -5743,12 +5684,12 @@
         <v>4</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39" spans="1:5" s="1" customFormat="1" ht="55.2">
       <c r="A39" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B39" s="8">
         <v>31</v>
@@ -5760,12 +5701,12 @@
         <v>4</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40" spans="1:5" s="1" customFormat="1" ht="55.2">
       <c r="A40" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B40" s="8">
         <v>31</v>
@@ -5777,12 +5718,12 @@
         <v>4</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41" spans="1:5" s="1" customFormat="1" ht="55.2">
       <c r="A41" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B41" s="8">
         <v>32</v>
@@ -5794,12 +5735,12 @@
         <v>4</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42" spans="1:5" s="1" customFormat="1" ht="55.2">
       <c r="A42" s="6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B42" s="8">
         <v>32</v>
@@ -5811,12 +5752,12 @@
         <v>4</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:5" s="1" customFormat="1" ht="55.2">
       <c r="A43" s="6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B43" s="8">
         <v>33</v>
@@ -5828,12 +5769,12 @@
         <v>4</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="44" spans="1:5" s="1" customFormat="1" ht="55.2">
       <c r="A44" s="6" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B44" s="8">
         <v>33</v>
@@ -5845,12 +5786,12 @@
         <v>4</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="45" spans="1:5" s="1" customFormat="1" ht="55.2">
       <c r="A45" s="25" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B45" s="8">
         <v>34</v>
@@ -5862,12 +5803,12 @@
         <v>4</v>
       </c>
       <c r="E45" s="21" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="46" spans="1:5" s="1" customFormat="1" ht="55.2">
       <c r="A46" s="23" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B46" s="8">
         <v>34</v>
@@ -5879,12 +5820,12 @@
         <v>4</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="47" spans="1:5" s="1" customFormat="1" ht="82.8">
       <c r="A47" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B47" s="8">
         <v>35</v>
@@ -5896,12 +5837,12 @@
         <v>4</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48" spans="1:5" s="1" customFormat="1" ht="115.95" customHeight="1">
       <c r="A48" s="24" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B48" s="8">
         <v>35</v>
@@ -5913,12 +5854,12 @@
         <v>4</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49" spans="1:5" s="1" customFormat="1" ht="55.2">
       <c r="A49" s="26" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B49" s="8">
         <v>36</v>
@@ -5930,12 +5871,12 @@
         <v>4</v>
       </c>
       <c r="E49" s="28" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:5" s="1" customFormat="1" ht="53.4" customHeight="1">
       <c r="A50" s="6" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B50" s="29">
         <v>48</v>
